--- a/data/trans_dic/P15E_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15E_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,55; 92,79</t>
+          <t>58,75; 93,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,1; 81,37</t>
+          <t>58,49; 81,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,03; 83,2</t>
+          <t>63,92; 82,96</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>32,22; 84,17</t>
+          <t>30,76; 84,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>56,55; 83,41</t>
+          <t>57,09; 82,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53,66; 79,7</t>
+          <t>55,28; 80,29</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,12; 100,0</t>
+          <t>11,14; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,71; 94,4</t>
+          <t>69,07; 94,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66,07; 91,32</t>
+          <t>65,51; 91,26</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,49; 76,15</t>
+          <t>25,73; 77,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,0; 74,59</t>
+          <t>42,96; 74,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,66; 70,19</t>
+          <t>42,23; 69,87</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>50,5; 76,16</t>
+          <t>50,07; 77,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>63,63; 78,28</t>
+          <t>64,85; 78,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,36; 75,95</t>
+          <t>63,4; 75,62</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año</t>
+          <t>Población mayor de 65 años que ha sufrido alguna caída que precise atención sanitaria en el último año (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7472; 11842</t>
+          <t>7497; 11874</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11952; 17032</t>
+          <t>12242; 17068</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21237; 28034</t>
+          <t>21536; 27951</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2598; 6786</t>
+          <t>2480; 6782</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12121; 17879</t>
+          <t>12238; 17790</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15828; 23510</t>
+          <t>16307; 23684</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>624; 3868</t>
+          <t>431; 3868</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15658; 20904</t>
+          <t>15296; 20957</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17187; 23755</t>
+          <t>17040; 23737</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2400; 7170</t>
+          <t>2423; 7337</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7635; 13560</t>
+          <t>7810; 13624</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11497; 19368</t>
+          <t>11652; 19281</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17224; 25976</t>
+          <t>17080; 26406</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52617; 64726</t>
+          <t>53627; 64833</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74001; 88709</t>
+          <t>74045; 88323</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15E_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P15E_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>75,28%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>58,75; 93,04</t>
+          <t>60,47; 93,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,49; 81,55</t>
+          <t>57,18; 82,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,92; 82,96</t>
+          <t>63,88; 84,0</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>69,43%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,76; 84,12</t>
+          <t>30,01; 84,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,09; 82,99</t>
+          <t>60,8; 84,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,28; 80,29</t>
+          <t>55,06; 80,38</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,81%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,14; 100,0</t>
+          <t>16,58; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>69,07; 94,64</t>
+          <t>71,19; 94,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,51; 91,26</t>
+          <t>65,93; 91,37</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,73; 77,92</t>
+          <t>23,33; 73,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,96; 74,94</t>
+          <t>41,14; 75,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,23; 69,87</t>
+          <t>41,02; 68,9</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,25%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>50,07; 77,42</t>
+          <t>50,16; 75,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,85; 78,41</t>
+          <t>65,92; 79,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,4; 75,62</t>
+          <t>64,34; 76,08</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25043</t>
+          <t>27366</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7497; 11874</t>
+          <t>8706; 13519</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12242; 17068</t>
+          <t>12554; 18070</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21536; 27951</t>
+          <t>23220; 30534</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15379</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>22117</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2480; 6782</t>
+          <t>2511; 7104</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12238; 17790</t>
+          <t>14282; 19962</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16307; 23684</t>
+          <t>17540; 25604</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>20602</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20785</t>
+          <t>23404</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>431; 3868</t>
+          <t>772; 4655</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15296; 20957</t>
+          <t>17305; 22942</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17040; 23737</t>
+          <t>19095; 26461</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>16409</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2423; 7337</t>
+          <t>2493; 7805</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7810; 13624</t>
+          <t>7923; 14491</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11652; 19281</t>
+          <t>12282; 20630</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>59616</t>
+          <t>64902</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81671</t>
+          <t>89295</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17080; 26406</t>
+          <t>19114; 28837</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>53627; 64833</t>
+          <t>58671; 70528</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74045; 88323</t>
+          <t>81785; 96701</t>
         </is>
       </c>
     </row>
